--- a/excel-files/PASIG/FRANCISCO LEGASPI MEMORIAL SCHOOL.xlsx
+++ b/excel-files/PASIG/FRANCISCO LEGASPI MEMORIAL SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="218" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D3CA4E9-53D2-4C40-B914-C36DC8B45E12}"/>
+  <xr:revisionPtr revIDLastSave="521" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B24E3E7F-20B9-49E7-99C1-02F4F29EB360}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="92">
   <si>
     <t>Grade Level</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>MAPEH</t>
+  </si>
+  <si>
+    <t>SDO</t>
   </si>
   <si>
     <t xml:space="preserve">Quantity based on Target ADM-SLM - Q1 </t>
@@ -3647,7 +3650,9 @@
       <c r="C8" s="1">
         <v>82</v>
       </c>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
       <c r="E8" s="1"/>
       <c r="F8" s="5"/>
       <c r="G8" s="3">
@@ -3669,7 +3674,9 @@
       <c r="C9" s="1">
         <v>82</v>
       </c>
-      <c r="D9" s="1"/>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
       <c r="E9" s="1"/>
       <c r="F9" s="5"/>
       <c r="G9" s="3">
@@ -3691,7 +3698,9 @@
       <c r="C10" s="1">
         <v>82</v>
       </c>
-      <c r="D10" s="1"/>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
       <c r="E10" s="1"/>
       <c r="F10" s="5"/>
       <c r="G10" s="3">
@@ -3713,7 +3722,9 @@
       <c r="C11" s="1">
         <v>82</v>
       </c>
-      <c r="D11" s="1"/>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="5"/>
       <c r="G11" s="3">
@@ -3735,7 +3746,9 @@
       <c r="C12" s="1">
         <v>82</v>
       </c>
-      <c r="D12" s="1"/>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="5"/>
       <c r="G12" s="3">
@@ -3762,7 +3775,9 @@
       <c r="C14" s="1">
         <v>99</v>
       </c>
-      <c r="D14" s="1"/>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
       <c r="E14" s="1"/>
       <c r="F14" s="5"/>
       <c r="G14" s="3">
@@ -3784,7 +3799,9 @@
       <c r="C15" s="1">
         <v>99</v>
       </c>
-      <c r="D15" s="1"/>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
       <c r="E15" s="1"/>
       <c r="F15" s="5"/>
       <c r="G15" s="3">
@@ -3806,7 +3823,9 @@
       <c r="C16" s="1">
         <v>99</v>
       </c>
-      <c r="D16" s="1"/>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
       <c r="E16" s="1"/>
       <c r="F16" s="5"/>
       <c r="G16" s="3">
@@ -3828,7 +3847,9 @@
       <c r="C17" s="1">
         <v>99</v>
       </c>
-      <c r="D17" s="1"/>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
       <c r="E17" s="1"/>
       <c r="F17" s="5"/>
       <c r="G17" s="3">
@@ -3850,7 +3871,9 @@
       <c r="C18" s="1">
         <v>99</v>
       </c>
-      <c r="D18" s="1"/>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
       <c r="E18" s="1"/>
       <c r="F18" s="5"/>
       <c r="G18" s="3">
@@ -3872,7 +3895,9 @@
       <c r="C19" s="1">
         <v>99</v>
       </c>
-      <c r="D19" s="1"/>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
       <c r="E19" s="1"/>
       <c r="F19" s="5"/>
       <c r="G19" s="3">
@@ -3904,7 +3929,9 @@
       <c r="C21" s="1">
         <v>98</v>
       </c>
-      <c r="D21" s="1"/>
+      <c r="D21" s="1">
+        <v>0</v>
+      </c>
       <c r="E21" s="1"/>
       <c r="F21" s="5"/>
       <c r="G21" s="3">
@@ -4094,7 +4121,9 @@
       <c r="C28" s="1">
         <v>98</v>
       </c>
-      <c r="D28" s="1"/>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
       <c r="E28" s="1"/>
       <c r="F28" s="5"/>
       <c r="G28" s="3">
@@ -4116,7 +4145,9 @@
       <c r="C29" s="1">
         <v>98</v>
       </c>
-      <c r="D29" s="1"/>
+      <c r="D29" s="1">
+        <v>0</v>
+      </c>
       <c r="E29" s="1"/>
       <c r="F29" s="5"/>
       <c r="G29" s="3">
@@ -4148,7 +4179,9 @@
       <c r="C31" s="1">
         <v>113</v>
       </c>
-      <c r="D31" s="1"/>
+      <c r="D31" s="1">
+        <v>0</v>
+      </c>
       <c r="E31" s="1"/>
       <c r="F31" s="5"/>
       <c r="G31" s="3">
@@ -4170,7 +4203,9 @@
       <c r="C32" s="1">
         <v>113</v>
       </c>
-      <c r="D32" s="1"/>
+      <c r="D32" s="1">
+        <v>0</v>
+      </c>
       <c r="E32" s="1"/>
       <c r="F32" s="5"/>
       <c r="G32" s="3">
@@ -4192,7 +4227,9 @@
       <c r="C33" s="1">
         <v>113</v>
       </c>
-      <c r="D33" s="1"/>
+      <c r="D33" s="1">
+        <v>0</v>
+      </c>
       <c r="E33" s="1"/>
       <c r="F33" s="5"/>
       <c r="G33" s="3">
@@ -4214,7 +4251,9 @@
       <c r="C34" s="1">
         <v>113</v>
       </c>
-      <c r="D34" s="1"/>
+      <c r="D34" s="1">
+        <v>0</v>
+      </c>
       <c r="E34" s="1"/>
       <c r="F34" s="5"/>
       <c r="G34" s="3">
@@ -4292,7 +4331,9 @@
       <c r="C37" s="1">
         <v>113</v>
       </c>
-      <c r="D37" s="1"/>
+      <c r="D37" s="1">
+        <v>0</v>
+      </c>
       <c r="E37" s="1"/>
       <c r="F37" s="5"/>
       <c r="G37" s="3">
@@ -4314,7 +4355,9 @@
       <c r="C38" s="1">
         <v>113</v>
       </c>
-      <c r="D38" s="1"/>
+      <c r="D38" s="1">
+        <v>0</v>
+      </c>
       <c r="E38" s="1"/>
       <c r="F38" s="5"/>
       <c r="G38" s="3">
@@ -4336,7 +4379,9 @@
       <c r="C39" s="1">
         <v>113</v>
       </c>
-      <c r="D39" s="1"/>
+      <c r="D39" s="1">
+        <v>0</v>
+      </c>
       <c r="E39" s="1"/>
       <c r="F39" s="5"/>
       <c r="G39" s="3">
@@ -4368,7 +4413,9 @@
       <c r="C41" s="1">
         <v>96</v>
       </c>
-      <c r="D41" s="1"/>
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
       <c r="E41" s="1"/>
       <c r="F41" s="5"/>
       <c r="G41" s="3">
@@ -4390,7 +4437,9 @@
       <c r="C42" s="1">
         <v>96</v>
       </c>
-      <c r="D42" s="1"/>
+      <c r="D42" s="1">
+        <v>0</v>
+      </c>
       <c r="E42" s="1"/>
       <c r="F42" s="5"/>
       <c r="G42" s="3">
@@ -4412,7 +4461,9 @@
       <c r="C43" s="1">
         <v>96</v>
       </c>
-      <c r="D43" s="1"/>
+      <c r="D43" s="1">
+        <v>0</v>
+      </c>
       <c r="E43" s="1"/>
       <c r="F43" s="5"/>
       <c r="G43" s="3">
@@ -4434,7 +4485,9 @@
       <c r="C44" s="1">
         <v>96</v>
       </c>
-      <c r="D44" s="1"/>
+      <c r="D44" s="1">
+        <v>0</v>
+      </c>
       <c r="E44" s="1"/>
       <c r="F44" s="5"/>
       <c r="G44" s="3">
@@ -4456,7 +4509,9 @@
       <c r="C45" s="1">
         <v>96</v>
       </c>
-      <c r="D45" s="1"/>
+      <c r="D45" s="1">
+        <v>0</v>
+      </c>
       <c r="E45" s="1"/>
       <c r="F45" s="5"/>
       <c r="G45" s="3">
@@ -4478,7 +4533,9 @@
       <c r="C46" s="1">
         <v>96</v>
       </c>
-      <c r="D46" s="1"/>
+      <c r="D46" s="1">
+        <v>0</v>
+      </c>
       <c r="E46" s="1"/>
       <c r="F46" s="5"/>
       <c r="G46" s="3">
@@ -4500,7 +4557,9 @@
       <c r="C47" s="1">
         <v>96</v>
       </c>
-      <c r="D47" s="1"/>
+      <c r="D47" s="1">
+        <v>0</v>
+      </c>
       <c r="E47" s="1"/>
       <c r="F47" s="5"/>
       <c r="G47" s="3">
@@ -4522,7 +4581,9 @@
       <c r="C48" s="1">
         <v>96</v>
       </c>
-      <c r="D48" s="1"/>
+      <c r="D48" s="1">
+        <v>0</v>
+      </c>
       <c r="E48" s="1"/>
       <c r="F48" s="5"/>
       <c r="G48" s="3">
@@ -4544,7 +4605,9 @@
       <c r="C49" s="1">
         <v>96</v>
       </c>
-      <c r="D49" s="1"/>
+      <c r="D49" s="1">
+        <v>0</v>
+      </c>
       <c r="E49" s="1"/>
       <c r="F49" s="5"/>
       <c r="G49" s="3">
@@ -5493,8 +5556,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5509,7 +5572,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5680,7 +5743,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="K3" s="34"/>
+      <c r="K3" s="34">
+        <v>0</v>
+      </c>
       <c r="L3" s="32"/>
       <c r="M3" s="34"/>
       <c r="N3" s="5">
@@ -5695,7 +5760,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="Q3" s="34"/>
+      <c r="Q3" s="34">
+        <v>0</v>
+      </c>
       <c r="R3" s="32"/>
       <c r="S3" s="34"/>
       <c r="T3" s="34">
@@ -5710,7 +5777,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>0</v>
       </c>
-      <c r="W3" s="34"/>
+      <c r="W3" s="34">
+        <v>0</v>
+      </c>
       <c r="X3" s="32"/>
       <c r="Y3" s="34"/>
       <c r="Z3" s="34">
@@ -5748,7 +5817,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
       <c r="F5" s="1"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
@@ -5763,7 +5834,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="K5" s="5"/>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5">
@@ -5778,7 +5851,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="Q5" s="5"/>
+      <c r="Q5" s="5">
+        <v>0</v>
+      </c>
       <c r="R5" s="1"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5">
@@ -5793,7 +5868,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="W5" s="5"/>
+      <c r="W5" s="5">
+        <v>0</v>
+      </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5">
@@ -5819,7 +5896,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
@@ -5834,7 +5913,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="K6" s="5"/>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
       <c r="L6" s="1"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5">
@@ -5849,7 +5930,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="Q6" s="5"/>
+      <c r="Q6" s="5">
+        <v>0</v>
+      </c>
       <c r="R6" s="1"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5">
@@ -5864,7 +5947,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="W6" s="5"/>
+      <c r="W6" s="5">
+        <v>0</v>
+      </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5">
@@ -5890,7 +5975,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5">
@@ -5905,7 +5992,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="K7" s="5"/>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
       <c r="L7" s="1"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5">
@@ -5920,7 +6009,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="Q7" s="5"/>
+      <c r="Q7" s="5">
+        <v>0</v>
+      </c>
       <c r="R7" s="1"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5">
@@ -5935,7 +6026,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="W7" s="5"/>
+      <c r="W7" s="5">
+        <v>0</v>
+      </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5">
@@ -5961,7 +6054,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
       <c r="F8" s="1"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
@@ -5976,7 +6071,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="K8" s="5"/>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
       <c r="L8" s="1"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5">
@@ -5991,7 +6088,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="Q8" s="5"/>
+      <c r="Q8" s="5">
+        <v>0</v>
+      </c>
       <c r="R8" s="1"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5">
@@ -6006,7 +6105,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="W8" s="5"/>
+      <c r="W8" s="5">
+        <v>0</v>
+      </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
@@ -6032,7 +6133,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
       <c r="F9" s="1"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5">
@@ -6047,7 +6150,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="K9" s="5"/>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
       <c r="L9" s="1"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5">
@@ -6062,7 +6167,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="Q9" s="5"/>
+      <c r="Q9" s="5">
+        <v>0</v>
+      </c>
       <c r="R9" s="1"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
@@ -6077,7 +6184,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="W9" s="5"/>
+      <c r="W9" s="5">
+        <v>0</v>
+      </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5">
@@ -6103,7 +6212,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
       <c r="F10" s="1"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
@@ -6118,7 +6229,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="K10" s="5"/>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
       <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
@@ -6133,7 +6246,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="Q10" s="5"/>
+      <c r="Q10" s="5">
+        <v>0</v>
+      </c>
       <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
@@ -6148,7 +6263,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="W10" s="5"/>
+      <c r="W10" s="5">
+        <v>0</v>
+      </c>
       <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
@@ -6174,7 +6291,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
       <c r="F11" s="1"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5">
@@ -6189,7 +6308,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="K11" s="5"/>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
       <c r="L11" s="1"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5">
@@ -6204,7 +6325,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="Q11" s="5"/>
+      <c r="Q11" s="5">
+        <v>0</v>
+      </c>
       <c r="R11" s="1"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5">
@@ -6219,7 +6342,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="W11" s="5"/>
+      <c r="W11" s="5">
+        <v>0</v>
+      </c>
       <c r="X11" s="1"/>
       <c r="Y11" s="5"/>
       <c r="Z11" s="5">
@@ -6245,7 +6370,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
       <c r="F12" s="1"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
@@ -6260,7 +6387,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="K12" s="5"/>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
       <c r="L12" s="1"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5">
@@ -6275,7 +6404,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="Q12" s="5"/>
+      <c r="Q12" s="5">
+        <v>0</v>
+      </c>
       <c r="R12" s="1"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5">
@@ -6290,7 +6421,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="W12" s="5"/>
+      <c r="W12" s="5">
+        <v>0</v>
+      </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5">
@@ -6329,7 +6462,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
@@ -6344,7 +6479,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="K14" s="5"/>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
       <c r="L14" s="1"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5">
@@ -6359,7 +6496,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="Q14" s="5"/>
+      <c r="Q14" s="5">
+        <v>0</v>
+      </c>
       <c r="R14" s="1"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5">
@@ -6374,7 +6513,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="W14" s="5"/>
+      <c r="W14" s="5">
+        <v>0</v>
+      </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5">
@@ -6400,7 +6541,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5">
@@ -6415,7 +6558,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="K15" s="5"/>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5">
@@ -6430,7 +6575,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="Q15" s="5"/>
+      <c r="Q15" s="5">
+        <v>0</v>
+      </c>
       <c r="R15" s="1"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5">
@@ -6445,7 +6592,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="W15" s="5"/>
+      <c r="W15" s="5">
+        <v>0</v>
+      </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5">
@@ -6474,8 +6623,12 @@
       <c r="E16" s="5">
         <v>103</v>
       </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="5"/>
+      <c r="F16" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H16" s="5">
         <f t="shared" si="2"/>
         <v>553</v>
@@ -6488,7 +6641,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="K16" s="5"/>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
       <c r="L16" s="1"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5">
@@ -6503,7 +6658,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="Q16" s="5"/>
+      <c r="Q16" s="5">
+        <v>0</v>
+      </c>
       <c r="R16" s="1"/>
       <c r="S16" s="5"/>
       <c r="T16" s="5">
@@ -6518,7 +6675,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="W16" s="5"/>
+      <c r="W16" s="5">
+        <v>0</v>
+      </c>
       <c r="X16" s="1"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5">
@@ -6547,8 +6706,12 @@
       <c r="E17" s="5">
         <v>103</v>
       </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="5"/>
+      <c r="F17" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H17" s="5">
         <f t="shared" si="2"/>
         <v>553</v>
@@ -6561,7 +6724,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="K17" s="5"/>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
       <c r="L17" s="1"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5">
@@ -6576,7 +6741,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="Q17" s="5"/>
+      <c r="Q17" s="5">
+        <v>0</v>
+      </c>
       <c r="R17" s="1"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
@@ -6591,7 +6758,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="W17" s="5"/>
+      <c r="W17" s="5">
+        <v>0</v>
+      </c>
       <c r="X17" s="1"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5">
@@ -6617,7 +6786,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="5">
+        <v>0</v>
+      </c>
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5">
@@ -6632,7 +6803,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="K18" s="5"/>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
       <c r="L18" s="1"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5">
@@ -6647,7 +6820,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="Q18" s="5"/>
+      <c r="Q18" s="5">
+        <v>0</v>
+      </c>
       <c r="R18" s="1"/>
       <c r="S18" s="5"/>
       <c r="T18" s="5">
@@ -6662,7 +6837,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="W18" s="5"/>
+      <c r="W18" s="5">
+        <v>0</v>
+      </c>
       <c r="X18" s="1"/>
       <c r="Y18" s="5"/>
       <c r="Z18" s="5">
@@ -6691,8 +6868,12 @@
       <c r="E19" s="5">
         <v>103</v>
       </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="5"/>
+      <c r="F19" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H19" s="5">
         <f>IF((D19-E19)&lt;0,0,(D19-E19))</f>
         <v>553</v>
@@ -6705,7 +6886,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="K19" s="5"/>
+      <c r="K19" s="5">
+        <v>0</v>
+      </c>
       <c r="L19" s="1"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5">
@@ -6720,7 +6903,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="Q19" s="5"/>
+      <c r="Q19" s="5">
+        <v>0</v>
+      </c>
       <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
@@ -6735,7 +6920,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="W19" s="5"/>
+      <c r="W19" s="5">
+        <v>0</v>
+      </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
@@ -6764,8 +6951,12 @@
       <c r="E20" s="5">
         <v>103</v>
       </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="5"/>
+      <c r="F20" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H20" s="5">
         <f>IF((D20-E20)&lt;0,0,(D20-E20))</f>
         <v>553</v>
@@ -6778,7 +6969,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="K20" s="5"/>
+      <c r="K20" s="5">
+        <v>0</v>
+      </c>
       <c r="L20" s="1"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5">
@@ -6793,7 +6986,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="Q20" s="5"/>
+      <c r="Q20" s="5">
+        <v>0</v>
+      </c>
       <c r="R20" s="1"/>
       <c r="S20" s="5"/>
       <c r="T20" s="5">
@@ -6808,7 +7003,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="W20" s="5"/>
+      <c r="W20" s="5">
+        <v>0</v>
+      </c>
       <c r="X20" s="1"/>
       <c r="Y20" s="5"/>
       <c r="Z20" s="5">
@@ -6834,7 +7031,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="5">
+        <v>0</v>
+      </c>
       <c r="F21" s="1"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5">
@@ -6849,7 +7048,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="K21" s="5"/>
+      <c r="K21" s="5">
+        <v>0</v>
+      </c>
       <c r="L21" s="1"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5">
@@ -6864,7 +7065,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="Q21" s="5"/>
+      <c r="Q21" s="5">
+        <v>0</v>
+      </c>
       <c r="R21" s="1"/>
       <c r="S21" s="5"/>
       <c r="T21" s="5">
@@ -6879,7 +7082,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="W21" s="5"/>
+      <c r="W21" s="5">
+        <v>0</v>
+      </c>
       <c r="X21" s="1"/>
       <c r="Y21" s="5"/>
       <c r="Z21" s="5">
@@ -6919,7 +7124,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="E23" s="5"/>
+      <c r="E23" s="5">
+        <v>0</v>
+      </c>
       <c r="F23" s="1"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5">
@@ -6934,7 +7141,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K23" s="5"/>
+      <c r="K23" s="5">
+        <v>0</v>
+      </c>
       <c r="L23" s="1"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5">
@@ -6949,7 +7158,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q23" s="5"/>
+      <c r="Q23" s="5">
+        <v>0</v>
+      </c>
       <c r="R23" s="1"/>
       <c r="S23" s="5"/>
       <c r="T23" s="5">
@@ -6964,7 +7175,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W23" s="5"/>
+      <c r="W23" s="5">
+        <v>0</v>
+      </c>
       <c r="X23" s="1"/>
       <c r="Y23" s="5"/>
       <c r="Z23" s="5">
@@ -6990,7 +7203,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="5">
+        <v>0</v>
+      </c>
       <c r="F24" s="1"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5">
@@ -7005,7 +7220,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K24" s="5"/>
+      <c r="K24" s="5">
+        <v>0</v>
+      </c>
       <c r="L24" s="1"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5">
@@ -7020,7 +7237,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q24" s="5"/>
+      <c r="Q24" s="5">
+        <v>0</v>
+      </c>
       <c r="R24" s="1"/>
       <c r="S24" s="5"/>
       <c r="T24" s="5">
@@ -7035,7 +7254,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W24" s="5"/>
+      <c r="W24" s="5">
+        <v>0</v>
+      </c>
       <c r="X24" s="1"/>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5">
@@ -7064,8 +7285,12 @@
       <c r="E25" s="5">
         <v>96</v>
       </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="5"/>
+      <c r="F25" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H25" s="5">
         <f t="shared" si="2"/>
         <v>696</v>
@@ -7078,7 +7303,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K25" s="5"/>
+      <c r="K25" s="5">
+        <v>0</v>
+      </c>
       <c r="L25" s="1"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5">
@@ -7093,7 +7320,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q25" s="5"/>
+      <c r="Q25" s="5">
+        <v>0</v>
+      </c>
       <c r="R25" s="1"/>
       <c r="S25" s="5"/>
       <c r="T25" s="5">
@@ -7108,7 +7337,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W25" s="5"/>
+      <c r="W25" s="5">
+        <v>0</v>
+      </c>
       <c r="X25" s="1"/>
       <c r="Y25" s="5"/>
       <c r="Z25" s="5">
@@ -7137,8 +7368,12 @@
       <c r="E26" s="5">
         <v>96</v>
       </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="5"/>
+      <c r="F26" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H26" s="5">
         <f t="shared" si="2"/>
         <v>696</v>
@@ -7151,7 +7386,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K26" s="5"/>
+      <c r="K26" s="5">
+        <v>0</v>
+      </c>
       <c r="L26" s="1"/>
       <c r="M26" s="5"/>
       <c r="N26" s="5">
@@ -7166,7 +7403,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q26" s="5"/>
+      <c r="Q26" s="5">
+        <v>0</v>
+      </c>
       <c r="R26" s="1"/>
       <c r="S26" s="5"/>
       <c r="T26" s="5">
@@ -7181,7 +7420,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W26" s="5"/>
+      <c r="W26" s="5">
+        <v>0</v>
+      </c>
       <c r="X26" s="1"/>
       <c r="Y26" s="5"/>
       <c r="Z26" s="5">
@@ -7210,8 +7451,12 @@
       <c r="E27" s="5">
         <v>96</v>
       </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="5"/>
+      <c r="F27" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H27" s="5">
         <f t="shared" si="2"/>
         <v>696</v>
@@ -7224,7 +7469,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K27" s="5"/>
+      <c r="K27" s="5">
+        <v>0</v>
+      </c>
       <c r="L27" s="1"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5">
@@ -7239,7 +7486,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q27" s="5"/>
+      <c r="Q27" s="5">
+        <v>0</v>
+      </c>
       <c r="R27" s="1"/>
       <c r="S27" s="5"/>
       <c r="T27" s="5">
@@ -7254,7 +7503,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W27" s="5"/>
+      <c r="W27" s="5">
+        <v>0</v>
+      </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="5"/>
       <c r="Z27" s="5">
@@ -7283,8 +7534,12 @@
       <c r="E28" s="5">
         <v>96</v>
       </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="5"/>
+      <c r="F28" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H28" s="5">
         <f t="shared" si="2"/>
         <v>696</v>
@@ -7297,7 +7552,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K28" s="5"/>
+      <c r="K28" s="5">
+        <v>0</v>
+      </c>
       <c r="L28" s="1"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5">
@@ -7312,7 +7569,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q28" s="5"/>
+      <c r="Q28" s="5">
+        <v>0</v>
+      </c>
       <c r="R28" s="1"/>
       <c r="S28" s="5"/>
       <c r="T28" s="5">
@@ -7327,7 +7586,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W28" s="5"/>
+      <c r="W28" s="5">
+        <v>0</v>
+      </c>
       <c r="X28" s="1"/>
       <c r="Y28" s="5"/>
       <c r="Z28" s="5">
@@ -7356,8 +7617,12 @@
       <c r="E29" s="5">
         <v>96</v>
       </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="5"/>
+      <c r="F29" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H29" s="5">
         <f>IF((D29-E29)&lt;0,0,(D29-E29))</f>
         <v>696</v>
@@ -7370,7 +7635,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K29" s="5"/>
+      <c r="K29" s="5">
+        <v>0</v>
+      </c>
       <c r="L29" s="1"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5">
@@ -7385,7 +7652,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q29" s="5"/>
+      <c r="Q29" s="5">
+        <v>0</v>
+      </c>
       <c r="R29" s="1"/>
       <c r="S29" s="5"/>
       <c r="T29" s="5">
@@ -7400,7 +7669,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W29" s="5"/>
+      <c r="W29" s="5">
+        <v>0</v>
+      </c>
       <c r="X29" s="1"/>
       <c r="Y29" s="5"/>
       <c r="Z29" s="5">
@@ -7429,8 +7700,12 @@
       <c r="E30" s="5">
         <v>96</v>
       </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="5"/>
+      <c r="F30" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H30" s="5">
         <f>IF((D30-E30)&lt;0,0,(D30-E30))</f>
         <v>696</v>
@@ -7443,7 +7718,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K30" s="5"/>
+      <c r="K30" s="5">
+        <v>0</v>
+      </c>
       <c r="L30" s="1"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5">
@@ -7458,7 +7735,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q30" s="5"/>
+      <c r="Q30" s="5">
+        <v>0</v>
+      </c>
       <c r="R30" s="1"/>
       <c r="S30" s="5"/>
       <c r="T30" s="5">
@@ -7473,7 +7752,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W30" s="5"/>
+      <c r="W30" s="5">
+        <v>0</v>
+      </c>
       <c r="X30" s="1"/>
       <c r="Y30" s="5"/>
       <c r="Z30" s="5">
@@ -7499,7 +7780,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="E31" s="5"/>
+      <c r="E31" s="5">
+        <v>0</v>
+      </c>
       <c r="F31" s="1"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5">
@@ -7514,7 +7797,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K31" s="5"/>
+      <c r="K31" s="5">
+        <v>0</v>
+      </c>
       <c r="L31" s="1"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5">
@@ -7529,7 +7814,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q31" s="5"/>
+      <c r="Q31" s="5">
+        <v>0</v>
+      </c>
       <c r="R31" s="1"/>
       <c r="S31" s="5"/>
       <c r="T31" s="5">
@@ -7544,7 +7831,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W31" s="5"/>
+      <c r="W31" s="5">
+        <v>0</v>
+      </c>
       <c r="X31" s="1"/>
       <c r="Y31" s="5"/>
       <c r="Z31" s="5">
@@ -7584,7 +7873,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E33" s="5"/>
+      <c r="E33" s="5">
+        <v>0</v>
+      </c>
       <c r="F33" s="1"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5">
@@ -7599,7 +7890,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K33" s="5"/>
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
       <c r="L33" s="1"/>
       <c r="M33" s="5"/>
       <c r="N33" s="5">
@@ -7614,7 +7907,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q33" s="5"/>
+      <c r="Q33" s="5">
+        <v>0</v>
+      </c>
       <c r="R33" s="1"/>
       <c r="S33" s="5"/>
       <c r="T33" s="5">
@@ -7629,7 +7924,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W33" s="5"/>
+      <c r="W33" s="5">
+        <v>0</v>
+      </c>
       <c r="X33" s="1"/>
       <c r="Y33" s="5"/>
       <c r="Z33" s="5">
@@ -7655,7 +7952,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E34" s="5"/>
+      <c r="E34" s="5">
+        <v>0</v>
+      </c>
       <c r="F34" s="1"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5">
@@ -7670,7 +7969,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K34" s="5"/>
+      <c r="K34" s="5">
+        <v>0</v>
+      </c>
       <c r="L34" s="1"/>
       <c r="M34" s="5"/>
       <c r="N34" s="5">
@@ -7685,7 +7986,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q34" s="5"/>
+      <c r="Q34" s="5">
+        <v>0</v>
+      </c>
       <c r="R34" s="1"/>
       <c r="S34" s="5"/>
       <c r="T34" s="5">
@@ -7700,7 +8003,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W34" s="5"/>
+      <c r="W34" s="5">
+        <v>0</v>
+      </c>
       <c r="X34" s="1"/>
       <c r="Y34" s="5"/>
       <c r="Z34" s="5">
@@ -7726,7 +8031,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E35" s="5"/>
+      <c r="E35" s="5">
+        <v>0</v>
+      </c>
       <c r="F35" s="1"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5">
@@ -7741,7 +8048,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K35" s="5"/>
+      <c r="K35" s="5">
+        <v>0</v>
+      </c>
       <c r="L35" s="1"/>
       <c r="M35" s="5"/>
       <c r="N35" s="5">
@@ -7756,7 +8065,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q35" s="5"/>
+      <c r="Q35" s="5">
+        <v>0</v>
+      </c>
       <c r="R35" s="1"/>
       <c r="S35" s="5"/>
       <c r="T35" s="5">
@@ -7771,7 +8082,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W35" s="5"/>
+      <c r="W35" s="5">
+        <v>0</v>
+      </c>
       <c r="X35" s="1"/>
       <c r="Y35" s="5"/>
       <c r="Z35" s="5">
@@ -7797,7 +8110,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E36" s="5"/>
+      <c r="E36" s="5">
+        <v>0</v>
+      </c>
       <c r="F36" s="1"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5">
@@ -7812,7 +8127,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K36" s="5"/>
+      <c r="K36" s="5">
+        <v>0</v>
+      </c>
       <c r="L36" s="1"/>
       <c r="M36" s="5"/>
       <c r="N36" s="5">
@@ -7827,7 +8144,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q36" s="5"/>
+      <c r="Q36" s="5">
+        <v>0</v>
+      </c>
       <c r="R36" s="1"/>
       <c r="S36" s="5"/>
       <c r="T36" s="5">
@@ -7842,7 +8161,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W36" s="5"/>
+      <c r="W36" s="5">
+        <v>0</v>
+      </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="5"/>
       <c r="Z36" s="5">
@@ -7868,7 +8189,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E37" s="5"/>
+      <c r="E37" s="5">
+        <v>0</v>
+      </c>
       <c r="F37" s="1"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5">
@@ -7883,7 +8206,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K37" s="5"/>
+      <c r="K37" s="5">
+        <v>0</v>
+      </c>
       <c r="L37" s="1"/>
       <c r="M37" s="5"/>
       <c r="N37" s="5">
@@ -7898,7 +8223,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q37" s="5"/>
+      <c r="Q37" s="5">
+        <v>0</v>
+      </c>
       <c r="R37" s="1"/>
       <c r="S37" s="5"/>
       <c r="T37" s="5">
@@ -7913,7 +8240,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W37" s="5"/>
+      <c r="W37" s="5">
+        <v>0</v>
+      </c>
       <c r="X37" s="1"/>
       <c r="Y37" s="5"/>
       <c r="Z37" s="5">
@@ -7939,7 +8268,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E38" s="5"/>
+      <c r="E38" s="5">
+        <v>0</v>
+      </c>
       <c r="F38" s="1"/>
       <c r="G38" s="5"/>
       <c r="H38" s="5">
@@ -7954,7 +8285,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K38" s="5"/>
+      <c r="K38" s="5">
+        <v>0</v>
+      </c>
       <c r="L38" s="1"/>
       <c r="M38" s="5"/>
       <c r="N38" s="5">
@@ -7969,7 +8302,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q38" s="5"/>
+      <c r="Q38" s="5">
+        <v>0</v>
+      </c>
       <c r="R38" s="1"/>
       <c r="S38" s="5"/>
       <c r="T38" s="5">
@@ -7984,7 +8319,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W38" s="5"/>
+      <c r="W38" s="5">
+        <v>0</v>
+      </c>
       <c r="X38" s="1"/>
       <c r="Y38" s="5"/>
       <c r="Z38" s="5">
@@ -8010,7 +8347,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E39" s="5"/>
+      <c r="E39" s="5">
+        <v>0</v>
+      </c>
       <c r="F39" s="1"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5">
@@ -8025,7 +8364,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K39" s="5"/>
+      <c r="K39" s="5">
+        <v>0</v>
+      </c>
       <c r="L39" s="1"/>
       <c r="M39" s="5"/>
       <c r="N39" s="5">
@@ -8040,7 +8381,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q39" s="5"/>
+      <c r="Q39" s="5">
+        <v>0</v>
+      </c>
       <c r="R39" s="1"/>
       <c r="S39" s="5"/>
       <c r="T39" s="5">
@@ -8055,7 +8398,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W39" s="5"/>
+      <c r="W39" s="5">
+        <v>0</v>
+      </c>
       <c r="X39" s="1"/>
       <c r="Y39" s="5"/>
       <c r="Z39" s="5">
@@ -8081,7 +8426,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E40" s="5"/>
+      <c r="E40" s="5">
+        <v>0</v>
+      </c>
       <c r="F40" s="1"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5">
@@ -8096,7 +8443,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K40" s="5"/>
+      <c r="K40" s="5">
+        <v>0</v>
+      </c>
       <c r="L40" s="1"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5">
@@ -8111,7 +8460,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q40" s="5"/>
+      <c r="Q40" s="5">
+        <v>0</v>
+      </c>
       <c r="R40" s="1"/>
       <c r="S40" s="5"/>
       <c r="T40" s="5">
@@ -8126,7 +8477,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W40" s="5"/>
+      <c r="W40" s="5">
+        <v>0</v>
+      </c>
       <c r="X40" s="1"/>
       <c r="Y40" s="5"/>
       <c r="Z40" s="5">
@@ -8152,7 +8505,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E41" s="5"/>
+      <c r="E41" s="5">
+        <v>0</v>
+      </c>
       <c r="F41" s="1"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5">
@@ -8167,7 +8522,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K41" s="5"/>
+      <c r="K41" s="5">
+        <v>0</v>
+      </c>
       <c r="L41" s="1"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5">
@@ -8182,7 +8539,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q41" s="5"/>
+      <c r="Q41" s="5">
+        <v>0</v>
+      </c>
       <c r="R41" s="1"/>
       <c r="S41" s="5"/>
       <c r="T41" s="5">
@@ -8197,7 +8556,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W41" s="5"/>
+      <c r="W41" s="5">
+        <v>0</v>
+      </c>
       <c r="X41" s="1"/>
       <c r="Y41" s="5"/>
       <c r="Z41" s="5">
@@ -8240,8 +8601,12 @@
       <c r="E43" s="5">
         <v>94</v>
       </c>
-      <c r="F43" s="1"/>
-      <c r="G43" s="5"/>
+      <c r="F43" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H43" s="5">
         <f t="shared" si="2"/>
         <v>810</v>
@@ -8254,7 +8619,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K43" s="5"/>
+      <c r="K43" s="5">
+        <v>0</v>
+      </c>
       <c r="L43" s="1"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5">
@@ -8269,7 +8636,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q43" s="5"/>
+      <c r="Q43" s="5">
+        <v>0</v>
+      </c>
       <c r="R43" s="1"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5">
@@ -8284,7 +8653,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W43" s="5"/>
+      <c r="W43" s="5">
+        <v>0</v>
+      </c>
       <c r="X43" s="1"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5">
@@ -8313,8 +8684,12 @@
       <c r="E44" s="5">
         <v>94</v>
       </c>
-      <c r="F44" s="1"/>
-      <c r="G44" s="5"/>
+      <c r="F44" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H44" s="5">
         <f t="shared" si="2"/>
         <v>810</v>
@@ -8327,7 +8702,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K44" s="5"/>
+      <c r="K44" s="5">
+        <v>0</v>
+      </c>
       <c r="L44" s="1"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5">
@@ -8342,7 +8719,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q44" s="5"/>
+      <c r="Q44" s="5">
+        <v>0</v>
+      </c>
       <c r="R44" s="1"/>
       <c r="S44" s="5"/>
       <c r="T44" s="5">
@@ -8357,7 +8736,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W44" s="5"/>
+      <c r="W44" s="5">
+        <v>0</v>
+      </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="5"/>
       <c r="Z44" s="5">
@@ -8386,8 +8767,12 @@
       <c r="E45" s="5">
         <v>94</v>
       </c>
-      <c r="F45" s="1"/>
-      <c r="G45" s="5"/>
+      <c r="F45" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H45" s="5">
         <f t="shared" si="2"/>
         <v>810</v>
@@ -8400,7 +8785,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K45" s="5"/>
+      <c r="K45" s="5">
+        <v>0</v>
+      </c>
       <c r="L45" s="1"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5">
@@ -8415,7 +8802,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q45" s="5"/>
+      <c r="Q45" s="5">
+        <v>0</v>
+      </c>
       <c r="R45" s="1"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5">
@@ -8430,7 +8819,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W45" s="5"/>
+      <c r="W45" s="5">
+        <v>0</v>
+      </c>
       <c r="X45" s="1"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5">
@@ -8459,8 +8850,12 @@
       <c r="E46" s="5">
         <v>94</v>
       </c>
-      <c r="F46" s="1"/>
-      <c r="G46" s="5"/>
+      <c r="F46" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H46" s="5">
         <f t="shared" si="2"/>
         <v>810</v>
@@ -8473,7 +8868,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K46" s="5"/>
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
       <c r="L46" s="1"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5">
@@ -8488,7 +8885,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q46" s="5"/>
+      <c r="Q46" s="5">
+        <v>0</v>
+      </c>
       <c r="R46" s="1"/>
       <c r="S46" s="5"/>
       <c r="T46" s="5">
@@ -8503,7 +8902,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W46" s="5"/>
+      <c r="W46" s="5">
+        <v>0</v>
+      </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="5"/>
       <c r="Z46" s="5">
@@ -8532,8 +8933,12 @@
       <c r="E47" s="5">
         <v>94</v>
       </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="5"/>
+      <c r="F47" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H47" s="5">
         <f t="shared" si="2"/>
         <v>810</v>
@@ -8546,7 +8951,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K47" s="5"/>
+      <c r="K47" s="5">
+        <v>0</v>
+      </c>
       <c r="L47" s="1"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5">
@@ -8561,7 +8968,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q47" s="5"/>
+      <c r="Q47" s="5">
+        <v>0</v>
+      </c>
       <c r="R47" s="1"/>
       <c r="S47" s="5"/>
       <c r="T47" s="5">
@@ -8576,7 +8985,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W47" s="5"/>
+      <c r="W47" s="5">
+        <v>0</v>
+      </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="5"/>
       <c r="Z47" s="5">
@@ -8602,7 +9013,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="E48" s="5"/>
+      <c r="E48" s="5">
+        <v>0</v>
+      </c>
       <c r="F48" s="1"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5">
@@ -8617,7 +9030,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K48" s="5"/>
+      <c r="K48" s="5">
+        <v>0</v>
+      </c>
       <c r="L48" s="1"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5">
@@ -8632,7 +9047,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q48" s="5"/>
+      <c r="Q48" s="5">
+        <v>0</v>
+      </c>
       <c r="R48" s="1"/>
       <c r="S48" s="5"/>
       <c r="T48" s="5">
@@ -8647,7 +9064,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W48" s="5"/>
+      <c r="W48" s="5">
+        <v>0</v>
+      </c>
       <c r="X48" s="1"/>
       <c r="Y48" s="5"/>
       <c r="Z48" s="5">
@@ -8676,8 +9095,12 @@
       <c r="E49" s="5">
         <v>94</v>
       </c>
-      <c r="F49" s="1"/>
-      <c r="G49" s="5"/>
+      <c r="F49" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H49" s="5">
         <f t="shared" si="2"/>
         <v>810</v>
@@ -8690,7 +9113,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K49" s="5"/>
+      <c r="K49" s="5">
+        <v>0</v>
+      </c>
       <c r="L49" s="1"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5">
@@ -8705,7 +9130,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q49" s="5"/>
+      <c r="Q49" s="5">
+        <v>0</v>
+      </c>
       <c r="R49" s="1"/>
       <c r="S49" s="5"/>
       <c r="T49" s="5">
@@ -8720,7 +9147,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W49" s="5"/>
+      <c r="W49" s="5">
+        <v>0</v>
+      </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="5"/>
       <c r="Z49" s="5">
@@ -8749,8 +9178,12 @@
       <c r="E50" s="5">
         <v>94</v>
       </c>
-      <c r="F50" s="1"/>
-      <c r="G50" s="5"/>
+      <c r="F50" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H50" s="5">
         <f t="shared" si="2"/>
         <v>810</v>
@@ -8763,7 +9196,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K50" s="5"/>
+      <c r="K50" s="5">
+        <v>0</v>
+      </c>
       <c r="L50" s="1"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5">
@@ -8778,7 +9213,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q50" s="5"/>
+      <c r="Q50" s="5">
+        <v>0</v>
+      </c>
       <c r="R50" s="1"/>
       <c r="S50" s="5"/>
       <c r="T50" s="5">
@@ -8793,7 +9230,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W50" s="5"/>
+      <c r="W50" s="5">
+        <v>0</v>
+      </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="5"/>
       <c r="Z50" s="5">
@@ -8822,8 +9261,12 @@
       <c r="E51" s="5">
         <v>94</v>
       </c>
-      <c r="F51" s="1"/>
-      <c r="G51" s="5"/>
+      <c r="F51" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="H51" s="5">
         <f t="shared" si="2"/>
         <v>810</v>
@@ -8836,7 +9279,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K51" s="5"/>
+      <c r="K51" s="5">
+        <v>0</v>
+      </c>
       <c r="L51" s="1"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5">
@@ -8851,7 +9296,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q51" s="5"/>
+      <c r="Q51" s="5">
+        <v>0</v>
+      </c>
       <c r="R51" s="1"/>
       <c r="S51" s="5"/>
       <c r="T51" s="5">
@@ -8866,7 +9313,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W51" s="5"/>
+      <c r="W51" s="5">
+        <v>0</v>
+      </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="5"/>
       <c r="Z51" s="5">
@@ -8878,7 +9327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8906,7 +9355,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E53" s="5"/>
+      <c r="E53" s="5">
+        <v>0</v>
+      </c>
       <c r="F53" s="1"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5">
@@ -8921,7 +9372,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K53" s="5"/>
+      <c r="K53" s="5">
+        <v>0</v>
+      </c>
       <c r="L53" s="1"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5">
@@ -8936,7 +9389,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q53" s="5"/>
+      <c r="Q53" s="5">
+        <v>0</v>
+      </c>
       <c r="R53" s="1"/>
       <c r="S53" s="5"/>
       <c r="T53" s="5">
@@ -8951,7 +9406,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W53" s="5"/>
+      <c r="W53" s="5">
+        <v>0</v>
+      </c>
       <c r="X53" s="1"/>
       <c r="Y53" s="5"/>
       <c r="Z53" s="5">
@@ -8977,7 +9434,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E54" s="5"/>
+      <c r="E54" s="5">
+        <v>0</v>
+      </c>
       <c r="F54" s="1"/>
       <c r="G54" s="5"/>
       <c r="H54" s="5">
@@ -8992,7 +9451,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K54" s="5"/>
+      <c r="K54" s="5">
+        <v>0</v>
+      </c>
       <c r="L54" s="1"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5">
@@ -9007,7 +9468,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q54" s="5"/>
+      <c r="Q54" s="5">
+        <v>0</v>
+      </c>
       <c r="R54" s="1"/>
       <c r="S54" s="5"/>
       <c r="T54" s="5">
@@ -9022,7 +9485,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W54" s="5"/>
+      <c r="W54" s="5">
+        <v>0</v>
+      </c>
       <c r="X54" s="1"/>
       <c r="Y54" s="5"/>
       <c r="Z54" s="5">
@@ -9048,7 +9513,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E55" s="5"/>
+      <c r="E55" s="5">
+        <v>0</v>
+      </c>
       <c r="F55" s="1"/>
       <c r="G55" s="5"/>
       <c r="H55" s="5">
@@ -9063,7 +9530,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K55" s="5"/>
+      <c r="K55" s="5">
+        <v>0</v>
+      </c>
       <c r="L55" s="1"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5">
@@ -9078,7 +9547,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q55" s="5"/>
+      <c r="Q55" s="5">
+        <v>0</v>
+      </c>
       <c r="R55" s="1"/>
       <c r="S55" s="5"/>
       <c r="T55" s="5">
@@ -9093,7 +9564,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W55" s="5"/>
+      <c r="W55" s="5">
+        <v>0</v>
+      </c>
       <c r="X55" s="1"/>
       <c r="Y55" s="5"/>
       <c r="Z55" s="5">
@@ -9119,7 +9592,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E56" s="5"/>
+      <c r="E56" s="5">
+        <v>0</v>
+      </c>
       <c r="F56" s="1"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5">
@@ -9134,7 +9609,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K56" s="5"/>
+      <c r="K56" s="5">
+        <v>0</v>
+      </c>
       <c r="L56" s="1"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5">
@@ -9149,7 +9626,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q56" s="5"/>
+      <c r="Q56" s="5">
+        <v>0</v>
+      </c>
       <c r="R56" s="1"/>
       <c r="S56" s="5"/>
       <c r="T56" s="5">
@@ -9164,7 +9643,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W56" s="5"/>
+      <c r="W56" s="5">
+        <v>0</v>
+      </c>
       <c r="X56" s="1"/>
       <c r="Y56" s="5"/>
       <c r="Z56" s="5">
@@ -9190,7 +9671,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E57" s="5"/>
+      <c r="E57" s="5">
+        <v>0</v>
+      </c>
       <c r="F57" s="1"/>
       <c r="G57" s="5"/>
       <c r="H57" s="5">
@@ -9205,7 +9688,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K57" s="5"/>
+      <c r="K57" s="5">
+        <v>0</v>
+      </c>
       <c r="L57" s="1"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5">
@@ -9220,7 +9705,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q57" s="5"/>
+      <c r="Q57" s="5">
+        <v>0</v>
+      </c>
       <c r="R57" s="1"/>
       <c r="S57" s="5"/>
       <c r="T57" s="5">
@@ -9235,7 +9722,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W57" s="5"/>
+      <c r="W57" s="5">
+        <v>0</v>
+      </c>
       <c r="X57" s="1"/>
       <c r="Y57" s="5"/>
       <c r="Z57" s="5">
@@ -9261,7 +9750,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E58" s="5"/>
+      <c r="E58" s="5">
+        <v>0</v>
+      </c>
       <c r="F58" s="1"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5">
@@ -9276,7 +9767,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K58" s="5"/>
+      <c r="K58" s="5">
+        <v>0</v>
+      </c>
       <c r="L58" s="1"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5">
@@ -9291,7 +9784,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q58" s="5"/>
+      <c r="Q58" s="5">
+        <v>0</v>
+      </c>
       <c r="R58" s="1"/>
       <c r="S58" s="5"/>
       <c r="T58" s="5">
@@ -9306,7 +9801,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W58" s="5"/>
+      <c r="W58" s="5">
+        <v>0</v>
+      </c>
       <c r="X58" s="1"/>
       <c r="Y58" s="5"/>
       <c r="Z58" s="5">
@@ -9332,7 +9829,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E59" s="5"/>
+      <c r="E59" s="5">
+        <v>0</v>
+      </c>
       <c r="F59" s="1"/>
       <c r="G59" s="5"/>
       <c r="H59" s="5">
@@ -9347,7 +9846,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K59" s="5"/>
+      <c r="K59" s="5">
+        <v>0</v>
+      </c>
       <c r="L59" s="1"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5">
@@ -9362,7 +9863,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q59" s="5"/>
+      <c r="Q59" s="5">
+        <v>0</v>
+      </c>
       <c r="R59" s="1"/>
       <c r="S59" s="5"/>
       <c r="T59" s="5">
@@ -9377,7 +9880,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W59" s="5"/>
+      <c r="W59" s="5">
+        <v>0</v>
+      </c>
       <c r="X59" s="1"/>
       <c r="Y59" s="5"/>
       <c r="Z59" s="5">
@@ -9403,7 +9908,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E60" s="5"/>
+      <c r="E60" s="5">
+        <v>0</v>
+      </c>
       <c r="F60" s="1"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5">
@@ -9418,7 +9925,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K60" s="5"/>
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
       <c r="L60" s="1"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5">
@@ -9433,7 +9942,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q60" s="5"/>
+      <c r="Q60" s="5">
+        <v>0</v>
+      </c>
       <c r="R60" s="1"/>
       <c r="S60" s="5"/>
       <c r="T60" s="5">
@@ -9448,7 +9959,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W60" s="5"/>
+      <c r="W60" s="5">
+        <v>0</v>
+      </c>
       <c r="X60" s="1"/>
       <c r="Y60" s="5"/>
       <c r="Z60" s="5">
@@ -9474,7 +9987,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E61" s="5"/>
+      <c r="E61" s="5">
+        <v>0</v>
+      </c>
       <c r="F61" s="1"/>
       <c r="G61" s="5"/>
       <c r="H61" s="5">
@@ -9489,7 +10004,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K61" s="5"/>
+      <c r="K61" s="5">
+        <v>0</v>
+      </c>
       <c r="L61" s="1"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5">
@@ -9504,7 +10021,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q61" s="5"/>
+      <c r="Q61" s="5">
+        <v>0</v>
+      </c>
       <c r="R61" s="1"/>
       <c r="S61" s="5"/>
       <c r="T61" s="5">
@@ -9519,7 +10038,9 @@
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W61" s="5"/>
+      <c r="W61" s="5">
+        <v>0</v>
+      </c>
       <c r="X61" s="1"/>
       <c r="Y61" s="5"/>
       <c r="Z61" s="5">
@@ -13637,191 +14158,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
-    <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
-    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
+    <protectedRange sqref="J2:L3 D2:F3 H5:L5 Q14:R21 W14:X21 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13 D14:F21 D23:F31 D43:F51" name="LAS"/>
+    <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G33:G41 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110 G23:G31 G43:G51" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="4">
@@ -13834,10 +14175,10 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R126 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 R127 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G103:G110 G33:G41 G23:G31 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G43:G51" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13853,7 +14194,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13927,76 +14268,76 @@
         <v>2</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G2" s="24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" s="22" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L2" s="23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="M2" s="40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N2" s="40" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O2" s="22" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R2" s="25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S2" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="T2" s="17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="U2" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V2" s="26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W2" s="26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X2" s="27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Y2" s="41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Z2" s="41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AA2" s="26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="38.25">
@@ -14013,7 +14354,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="5">
+        <v>0</v>
+      </c>
       <c r="F3" s="1"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5">
@@ -14028,7 +14371,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="K3" s="5"/>
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
       <c r="L3" s="1"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5">
@@ -14043,7 +14388,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="Q3" s="5"/>
+      <c r="Q3" s="5">
+        <v>0</v>
+      </c>
       <c r="R3" s="1"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5">
@@ -14058,7 +14405,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="W3" s="5"/>
+      <c r="W3" s="5">
+        <v>0</v>
+      </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="5"/>
       <c r="Z3" s="5">
@@ -14084,7 +14433,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
       <c r="F4" s="1"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5">
@@ -14099,7 +14450,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="K4" s="5"/>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
       <c r="L4" s="1"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5">
@@ -14114,7 +14467,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="Q4" s="5"/>
+      <c r="Q4" s="5">
+        <v>0</v>
+      </c>
       <c r="R4" s="1"/>
       <c r="S4" s="5"/>
       <c r="T4" s="5">
@@ -14129,7 +14484,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="W4" s="5"/>
+      <c r="W4" s="5">
+        <v>0</v>
+      </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="5"/>
       <c r="Z4" s="5">
@@ -14155,7 +14512,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
       <c r="F5" s="1"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
@@ -14170,7 +14529,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="K5" s="5"/>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
       <c r="L5" s="1"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5">
@@ -14185,7 +14546,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="Q5" s="5"/>
+      <c r="Q5" s="5">
+        <v>0</v>
+      </c>
       <c r="R5" s="1"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5">
@@ -14200,7 +14563,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="W5" s="5"/>
+      <c r="W5" s="5">
+        <v>0</v>
+      </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5">
@@ -14226,7 +14591,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
       <c r="F6" s="1"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
@@ -14241,7 +14608,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="K6" s="5"/>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
       <c r="L6" s="1"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5">
@@ -14256,7 +14625,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="Q6" s="5"/>
+      <c r="Q6" s="5">
+        <v>0</v>
+      </c>
       <c r="R6" s="1"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5">
@@ -14271,7 +14642,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="W6" s="5"/>
+      <c r="W6" s="5">
+        <v>0</v>
+      </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5">
@@ -14297,7 +14670,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5">
@@ -14312,7 +14687,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="K7" s="5"/>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
       <c r="L7" s="1"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5">
@@ -14327,7 +14704,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="Q7" s="5"/>
+      <c r="Q7" s="5">
+        <v>0</v>
+      </c>
       <c r="R7" s="1"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5">
@@ -14342,7 +14721,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="W7" s="5"/>
+      <c r="W7" s="5">
+        <v>0</v>
+      </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5">
@@ -14368,7 +14749,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
       <c r="F8" s="1"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
@@ -14383,7 +14766,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="K8" s="5"/>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
       <c r="L8" s="1"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5">
@@ -14398,7 +14783,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="Q8" s="5"/>
+      <c r="Q8" s="5">
+        <v>0</v>
+      </c>
       <c r="R8" s="1"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5">
@@ -14413,7 +14800,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="W8" s="5"/>
+      <c r="W8" s="5">
+        <v>0</v>
+      </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
@@ -14439,7 +14828,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
       <c r="F9" s="1"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5">
@@ -14454,7 +14845,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="K9" s="5"/>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
       <c r="L9" s="1"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5">
@@ -14469,7 +14862,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="Q9" s="5"/>
+      <c r="Q9" s="5">
+        <v>0</v>
+      </c>
       <c r="R9" s="1"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
@@ -14484,7 +14879,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="W9" s="5"/>
+      <c r="W9" s="5">
+        <v>0</v>
+      </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5">
@@ -14510,7 +14907,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
       <c r="F10" s="1"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
@@ -14525,7 +14924,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="K10" s="5"/>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
       <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
@@ -14540,7 +14941,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="Q10" s="5"/>
+      <c r="Q10" s="5">
+        <v>0</v>
+      </c>
       <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
@@ -14555,7 +14958,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>704</v>
       </c>
-      <c r="W10" s="5"/>
+      <c r="W10" s="5">
+        <v>0</v>
+      </c>
       <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
@@ -14582,7 +14987,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
       <c r="F12" s="1"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
@@ -14597,7 +15004,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="K12" s="5"/>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
       <c r="L12" s="1"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5">
@@ -14612,7 +15021,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="Q12" s="5"/>
+      <c r="Q12" s="5">
+        <v>0</v>
+      </c>
       <c r="R12" s="1"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5">
@@ -14627,7 +15038,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="W12" s="5"/>
+      <c r="W12" s="5">
+        <v>0</v>
+      </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5">
@@ -14653,7 +15066,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
       <c r="F13" s="1"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5">
@@ -14668,7 +15083,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="K13" s="5"/>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
       <c r="L13" s="1"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5">
@@ -14683,7 +15100,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="Q13" s="5"/>
+      <c r="Q13" s="5">
+        <v>0</v>
+      </c>
       <c r="R13" s="1"/>
       <c r="S13" s="5"/>
       <c r="T13" s="5">
@@ -14698,7 +15117,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="W13" s="5"/>
+      <c r="W13" s="5">
+        <v>0</v>
+      </c>
       <c r="X13" s="1"/>
       <c r="Y13" s="5"/>
       <c r="Z13" s="5">
@@ -14724,7 +15145,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
@@ -14739,7 +15162,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="K14" s="5"/>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
       <c r="L14" s="1"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5">
@@ -14754,7 +15179,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="Q14" s="5"/>
+      <c r="Q14" s="5">
+        <v>0</v>
+      </c>
       <c r="R14" s="1"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5">
@@ -14769,7 +15196,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="W14" s="5"/>
+      <c r="W14" s="5">
+        <v>0</v>
+      </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5">
@@ -14795,7 +15224,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5">
@@ -14810,7 +15241,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="K15" s="5"/>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
       <c r="L15" s="1"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5">
@@ -14825,7 +15258,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="Q15" s="5"/>
+      <c r="Q15" s="5">
+        <v>0</v>
+      </c>
       <c r="R15" s="1"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5">
@@ -14840,7 +15275,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="W15" s="5"/>
+      <c r="W15" s="5">
+        <v>0</v>
+      </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5">
@@ -14866,7 +15303,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
       <c r="F16" s="1"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5">
@@ -14881,7 +15320,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="K16" s="5"/>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
       <c r="L16" s="1"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5">
@@ -14896,7 +15337,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="Q16" s="5"/>
+      <c r="Q16" s="5">
+        <v>0</v>
+      </c>
       <c r="R16" s="1"/>
       <c r="S16" s="5"/>
       <c r="T16" s="5">
@@ -14911,7 +15354,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="W16" s="5"/>
+      <c r="W16" s="5">
+        <v>0</v>
+      </c>
       <c r="X16" s="1"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5">
@@ -14937,7 +15382,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="E17" s="5"/>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5">
@@ -14952,7 +15399,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="K17" s="5"/>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
       <c r="L17" s="1"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5">
@@ -14967,7 +15416,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="Q17" s="5"/>
+      <c r="Q17" s="5">
+        <v>0</v>
+      </c>
       <c r="R17" s="1"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
@@ -14982,7 +15433,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="W17" s="5"/>
+      <c r="W17" s="5">
+        <v>0</v>
+      </c>
       <c r="X17" s="1"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5">
@@ -15008,7 +15461,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="5">
+        <v>0</v>
+      </c>
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5">
@@ -15023,7 +15478,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="K18" s="5"/>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
       <c r="L18" s="1"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5">
@@ -15038,7 +15495,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="Q18" s="5"/>
+      <c r="Q18" s="5">
+        <v>0</v>
+      </c>
       <c r="R18" s="1"/>
       <c r="S18" s="5"/>
       <c r="T18" s="5">
@@ -15053,7 +15512,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="W18" s="5"/>
+      <c r="W18" s="5">
+        <v>0</v>
+      </c>
       <c r="X18" s="1"/>
       <c r="Y18" s="5"/>
       <c r="Z18" s="5">
@@ -15079,7 +15540,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="E19" s="5">
+        <v>0</v>
+      </c>
       <c r="F19" s="1"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
@@ -15094,7 +15557,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="K19" s="5"/>
+      <c r="K19" s="5">
+        <v>0</v>
+      </c>
       <c r="L19" s="1"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5">
@@ -15109,7 +15574,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="Q19" s="5"/>
+      <c r="Q19" s="5">
+        <v>0</v>
+      </c>
       <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
@@ -15124,7 +15591,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>656</v>
       </c>
-      <c r="W19" s="5"/>
+      <c r="W19" s="5">
+        <v>0</v>
+      </c>
       <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
@@ -15151,7 +15620,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="5">
+        <v>0</v>
+      </c>
       <c r="F21" s="1"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5">
@@ -15166,7 +15637,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K21" s="5"/>
+      <c r="K21" s="5">
+        <v>0</v>
+      </c>
       <c r="L21" s="1"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5">
@@ -15181,7 +15654,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q21" s="5"/>
+      <c r="Q21" s="5">
+        <v>0</v>
+      </c>
       <c r="R21" s="1"/>
       <c r="S21" s="5"/>
       <c r="T21" s="5">
@@ -15196,7 +15671,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W21" s="5"/>
+      <c r="W21" s="5">
+        <v>0</v>
+      </c>
       <c r="X21" s="1"/>
       <c r="Y21" s="5"/>
       <c r="Z21" s="5">
@@ -15222,7 +15699,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="E22" s="5"/>
+      <c r="E22" s="5">
+        <v>0</v>
+      </c>
       <c r="F22" s="1"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5">
@@ -15237,7 +15716,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K22" s="5"/>
+      <c r="K22" s="5">
+        <v>0</v>
+      </c>
       <c r="L22" s="1"/>
       <c r="M22" s="5"/>
       <c r="N22" s="5">
@@ -15252,7 +15733,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q22" s="5"/>
+      <c r="Q22" s="5">
+        <v>0</v>
+      </c>
       <c r="R22" s="1"/>
       <c r="S22" s="5"/>
       <c r="T22" s="5">
@@ -15267,7 +15750,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W22" s="5"/>
+      <c r="W22" s="5">
+        <v>0</v>
+      </c>
       <c r="X22" s="1"/>
       <c r="Y22" s="5"/>
       <c r="Z22" s="5">
@@ -15293,7 +15778,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="E23" s="5"/>
+      <c r="E23" s="5">
+        <v>0</v>
+      </c>
       <c r="F23" s="1"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5">
@@ -15308,7 +15795,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K23" s="5"/>
+      <c r="K23" s="5">
+        <v>0</v>
+      </c>
       <c r="L23" s="1"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5">
@@ -15323,7 +15812,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q23" s="5"/>
+      <c r="Q23" s="5">
+        <v>0</v>
+      </c>
       <c r="R23" s="1"/>
       <c r="S23" s="5"/>
       <c r="T23" s="5">
@@ -15338,7 +15829,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W23" s="5"/>
+      <c r="W23" s="5">
+        <v>0</v>
+      </c>
       <c r="X23" s="1"/>
       <c r="Y23" s="5"/>
       <c r="Z23" s="5">
@@ -15364,7 +15857,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="5">
+        <v>0</v>
+      </c>
       <c r="F24" s="1"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5">
@@ -15379,7 +15874,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K24" s="5"/>
+      <c r="K24" s="5">
+        <v>0</v>
+      </c>
       <c r="L24" s="1"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5">
@@ -15394,7 +15891,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q24" s="5"/>
+      <c r="Q24" s="5">
+        <v>0</v>
+      </c>
       <c r="R24" s="1"/>
       <c r="S24" s="5"/>
       <c r="T24" s="5">
@@ -15409,7 +15908,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W24" s="5"/>
+      <c r="W24" s="5">
+        <v>0</v>
+      </c>
       <c r="X24" s="1"/>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5">
@@ -15435,7 +15936,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="E25" s="5"/>
+      <c r="E25" s="5">
+        <v>0</v>
+      </c>
       <c r="F25" s="1"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5">
@@ -15450,7 +15953,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K25" s="5"/>
+      <c r="K25" s="5">
+        <v>0</v>
+      </c>
       <c r="L25" s="1"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5">
@@ -15465,7 +15970,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q25" s="5"/>
+      <c r="Q25" s="5">
+        <v>0</v>
+      </c>
       <c r="R25" s="1"/>
       <c r="S25" s="5"/>
       <c r="T25" s="5">
@@ -15480,7 +15987,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W25" s="5"/>
+      <c r="W25" s="5">
+        <v>0</v>
+      </c>
       <c r="X25" s="1"/>
       <c r="Y25" s="5"/>
       <c r="Z25" s="5">
@@ -15506,7 +16015,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="E26" s="5"/>
+      <c r="E26" s="5">
+        <v>0</v>
+      </c>
       <c r="F26" s="1"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5">
@@ -15521,7 +16032,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K26" s="5"/>
+      <c r="K26" s="5">
+        <v>0</v>
+      </c>
       <c r="L26" s="1"/>
       <c r="M26" s="5"/>
       <c r="N26" s="5">
@@ -15536,7 +16049,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q26" s="5"/>
+      <c r="Q26" s="5">
+        <v>0</v>
+      </c>
       <c r="R26" s="1"/>
       <c r="S26" s="5"/>
       <c r="T26" s="5">
@@ -15551,7 +16066,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W26" s="5"/>
+      <c r="W26" s="5">
+        <v>0</v>
+      </c>
       <c r="X26" s="1"/>
       <c r="Y26" s="5"/>
       <c r="Z26" s="5">
@@ -15577,7 +16094,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="E27" s="5"/>
+      <c r="E27" s="5">
+        <v>0</v>
+      </c>
       <c r="F27" s="1"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5">
@@ -15592,7 +16111,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K27" s="5"/>
+      <c r="K27" s="5">
+        <v>0</v>
+      </c>
       <c r="L27" s="1"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5">
@@ -15607,7 +16128,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q27" s="5"/>
+      <c r="Q27" s="5">
+        <v>0</v>
+      </c>
       <c r="R27" s="1"/>
       <c r="S27" s="5"/>
       <c r="T27" s="5">
@@ -15622,7 +16145,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W27" s="5"/>
+      <c r="W27" s="5">
+        <v>0</v>
+      </c>
       <c r="X27" s="1"/>
       <c r="Y27" s="5"/>
       <c r="Z27" s="5">
@@ -15648,7 +16173,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="E28" s="5"/>
+      <c r="E28" s="5">
+        <v>0</v>
+      </c>
       <c r="F28" s="1"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5">
@@ -15663,7 +16190,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K28" s="5"/>
+      <c r="K28" s="5">
+        <v>0</v>
+      </c>
       <c r="L28" s="1"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5">
@@ -15678,7 +16207,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q28" s="5"/>
+      <c r="Q28" s="5">
+        <v>0</v>
+      </c>
       <c r="R28" s="1"/>
       <c r="S28" s="5"/>
       <c r="T28" s="5">
@@ -15693,7 +16224,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W28" s="5"/>
+      <c r="W28" s="5">
+        <v>0</v>
+      </c>
       <c r="X28" s="1"/>
       <c r="Y28" s="5"/>
       <c r="Z28" s="5">
@@ -15719,7 +16252,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="E29" s="5"/>
+      <c r="E29" s="5">
+        <v>0</v>
+      </c>
       <c r="F29" s="1"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5">
@@ -15734,7 +16269,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="K29" s="5"/>
+      <c r="K29" s="5">
+        <v>0</v>
+      </c>
       <c r="L29" s="1"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5">
@@ -15749,7 +16286,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="Q29" s="5"/>
+      <c r="Q29" s="5">
+        <v>0</v>
+      </c>
       <c r="R29" s="1"/>
       <c r="S29" s="5"/>
       <c r="T29" s="5">
@@ -15764,7 +16303,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>792</v>
       </c>
-      <c r="W29" s="5"/>
+      <c r="W29" s="5">
+        <v>0</v>
+      </c>
       <c r="X29" s="1"/>
       <c r="Y29" s="5"/>
       <c r="Z29" s="5">
@@ -15791,7 +16332,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E31" s="5"/>
+      <c r="E31" s="5">
+        <v>0</v>
+      </c>
       <c r="F31" s="1"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5">
@@ -15806,7 +16349,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K31" s="5"/>
+      <c r="K31" s="5">
+        <v>0</v>
+      </c>
       <c r="L31" s="1"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5">
@@ -15821,7 +16366,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q31" s="5"/>
+      <c r="Q31" s="5">
+        <v>0</v>
+      </c>
       <c r="R31" s="1"/>
       <c r="S31" s="5"/>
       <c r="T31" s="5">
@@ -15836,7 +16383,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W31" s="5"/>
+      <c r="W31" s="5">
+        <v>0</v>
+      </c>
       <c r="X31" s="1"/>
       <c r="Y31" s="5"/>
       <c r="Z31" s="5">
@@ -15862,7 +16411,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E32" s="5"/>
+      <c r="E32" s="5">
+        <v>0</v>
+      </c>
       <c r="F32" s="1"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5">
@@ -15877,7 +16428,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K32" s="5"/>
+      <c r="K32" s="5">
+        <v>0</v>
+      </c>
       <c r="L32" s="1"/>
       <c r="M32" s="5"/>
       <c r="N32" s="5">
@@ -15892,7 +16445,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q32" s="5"/>
+      <c r="Q32" s="5">
+        <v>0</v>
+      </c>
       <c r="R32" s="1"/>
       <c r="S32" s="5"/>
       <c r="T32" s="5">
@@ -15907,7 +16462,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W32" s="5"/>
+      <c r="W32" s="5">
+        <v>0</v>
+      </c>
       <c r="X32" s="1"/>
       <c r="Y32" s="5"/>
       <c r="Z32" s="5">
@@ -15933,7 +16490,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E33" s="5"/>
+      <c r="E33" s="5">
+        <v>0</v>
+      </c>
       <c r="F33" s="1"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5">
@@ -15948,7 +16507,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K33" s="5"/>
+      <c r="K33" s="5">
+        <v>0</v>
+      </c>
       <c r="L33" s="1"/>
       <c r="M33" s="5"/>
       <c r="N33" s="5">
@@ -15963,7 +16524,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q33" s="5"/>
+      <c r="Q33" s="5">
+        <v>0</v>
+      </c>
       <c r="R33" s="1"/>
       <c r="S33" s="5"/>
       <c r="T33" s="5">
@@ -15978,7 +16541,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W33" s="5"/>
+      <c r="W33" s="5">
+        <v>0</v>
+      </c>
       <c r="X33" s="1"/>
       <c r="Y33" s="5"/>
       <c r="Z33" s="5">
@@ -16004,7 +16569,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E34" s="5"/>
+      <c r="E34" s="5">
+        <v>0</v>
+      </c>
       <c r="F34" s="1"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5">
@@ -16019,7 +16586,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K34" s="5"/>
+      <c r="K34" s="5">
+        <v>0</v>
+      </c>
       <c r="L34" s="1"/>
       <c r="M34" s="5"/>
       <c r="N34" s="5">
@@ -16034,7 +16603,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q34" s="5"/>
+      <c r="Q34" s="5">
+        <v>0</v>
+      </c>
       <c r="R34" s="1"/>
       <c r="S34" s="5"/>
       <c r="T34" s="5">
@@ -16049,7 +16620,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W34" s="5"/>
+      <c r="W34" s="5">
+        <v>0</v>
+      </c>
       <c r="X34" s="1"/>
       <c r="Y34" s="5"/>
       <c r="Z34" s="5">
@@ -16075,7 +16648,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E35" s="5"/>
+      <c r="E35" s="5">
+        <v>0</v>
+      </c>
       <c r="F35" s="1"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5">
@@ -16090,7 +16665,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K35" s="5"/>
+      <c r="K35" s="5">
+        <v>0</v>
+      </c>
       <c r="L35" s="1"/>
       <c r="M35" s="5"/>
       <c r="N35" s="5">
@@ -16105,7 +16682,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q35" s="5"/>
+      <c r="Q35" s="5">
+        <v>0</v>
+      </c>
       <c r="R35" s="1"/>
       <c r="S35" s="5"/>
       <c r="T35" s="5">
@@ -16120,7 +16699,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W35" s="5"/>
+      <c r="W35" s="5">
+        <v>0</v>
+      </c>
       <c r="X35" s="1"/>
       <c r="Y35" s="5"/>
       <c r="Z35" s="5">
@@ -16146,7 +16727,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E36" s="5"/>
+      <c r="E36" s="5">
+        <v>0</v>
+      </c>
       <c r="F36" s="1"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5">
@@ -16161,7 +16744,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K36" s="5"/>
+      <c r="K36" s="5">
+        <v>0</v>
+      </c>
       <c r="L36" s="1"/>
       <c r="M36" s="5"/>
       <c r="N36" s="5">
@@ -16176,7 +16761,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q36" s="5"/>
+      <c r="Q36" s="5">
+        <v>0</v>
+      </c>
       <c r="R36" s="1"/>
       <c r="S36" s="5"/>
       <c r="T36" s="5">
@@ -16191,7 +16778,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W36" s="5"/>
+      <c r="W36" s="5">
+        <v>0</v>
+      </c>
       <c r="X36" s="1"/>
       <c r="Y36" s="5"/>
       <c r="Z36" s="5">
@@ -16208,7 +16797,7 @@
         <v>4</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C37" s="5">
         <v>98</v>
@@ -16217,7 +16806,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E37" s="5"/>
+      <c r="E37" s="5">
+        <v>0</v>
+      </c>
       <c r="F37" s="1"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5">
@@ -16232,7 +16823,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K37" s="5"/>
+      <c r="K37" s="5">
+        <v>0</v>
+      </c>
       <c r="L37" s="1"/>
       <c r="M37" s="5"/>
       <c r="N37" s="5">
@@ -16247,7 +16840,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q37" s="5"/>
+      <c r="Q37" s="5">
+        <v>0</v>
+      </c>
       <c r="R37" s="1"/>
       <c r="S37" s="5"/>
       <c r="T37" s="5">
@@ -16262,7 +16857,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W37" s="5"/>
+      <c r="W37" s="5">
+        <v>0</v>
+      </c>
       <c r="X37" s="1"/>
       <c r="Y37" s="5"/>
       <c r="Z37" s="5">
@@ -16279,7 +16876,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C38" s="1">
         <v>98</v>
@@ -16288,7 +16885,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E38" s="5"/>
+      <c r="E38" s="5">
+        <v>0</v>
+      </c>
       <c r="F38" s="1"/>
       <c r="G38" s="5"/>
       <c r="H38" s="5">
@@ -16303,7 +16902,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K38" s="5"/>
+      <c r="K38" s="5">
+        <v>0</v>
+      </c>
       <c r="L38" s="1"/>
       <c r="M38" s="5"/>
       <c r="N38" s="5">
@@ -16318,7 +16919,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q38" s="5"/>
+      <c r="Q38" s="5">
+        <v>0</v>
+      </c>
       <c r="R38" s="1"/>
       <c r="S38" s="5"/>
       <c r="T38" s="5">
@@ -16333,7 +16936,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W38" s="5"/>
+      <c r="W38" s="5">
+        <v>0</v>
+      </c>
       <c r="X38" s="1"/>
       <c r="Y38" s="5"/>
       <c r="Z38" s="5">
@@ -16359,7 +16964,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E39" s="5"/>
+      <c r="E39" s="5">
+        <v>0</v>
+      </c>
       <c r="F39" s="1"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5">
@@ -16374,7 +16981,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K39" s="5"/>
+      <c r="K39" s="5">
+        <v>0</v>
+      </c>
       <c r="L39" s="1"/>
       <c r="M39" s="5"/>
       <c r="N39" s="5">
@@ -16389,7 +16998,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q39" s="5"/>
+      <c r="Q39" s="5">
+        <v>0</v>
+      </c>
       <c r="R39" s="1"/>
       <c r="S39" s="5"/>
       <c r="T39" s="5">
@@ -16404,7 +17015,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W39" s="5"/>
+      <c r="W39" s="5">
+        <v>0</v>
+      </c>
       <c r="X39" s="1"/>
       <c r="Y39" s="5"/>
       <c r="Z39" s="5">
@@ -16421,7 +17034,7 @@
         <v>4</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C40" s="5">
         <v>98</v>
@@ -16430,7 +17043,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E40" s="5"/>
+      <c r="E40" s="5">
+        <v>0</v>
+      </c>
       <c r="F40" s="1"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5">
@@ -16445,7 +17060,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K40" s="5"/>
+      <c r="K40" s="5">
+        <v>0</v>
+      </c>
       <c r="L40" s="1"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5">
@@ -16460,7 +17077,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q40" s="5"/>
+      <c r="Q40" s="5">
+        <v>0</v>
+      </c>
       <c r="R40" s="1"/>
       <c r="S40" s="5"/>
       <c r="T40" s="5">
@@ -16475,7 +17094,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W40" s="5"/>
+      <c r="W40" s="5">
+        <v>0</v>
+      </c>
       <c r="X40" s="1"/>
       <c r="Y40" s="5"/>
       <c r="Z40" s="5">
@@ -16492,7 +17113,7 @@
         <v>4</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C41" s="1">
         <v>98</v>
@@ -16501,7 +17122,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="E41" s="5"/>
+      <c r="E41" s="5">
+        <v>0</v>
+      </c>
       <c r="F41" s="1"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5">
@@ -16516,7 +17139,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="K41" s="5"/>
+      <c r="K41" s="5">
+        <v>0</v>
+      </c>
       <c r="L41" s="1"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5">
@@ -16531,7 +17156,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="Q41" s="5"/>
+      <c r="Q41" s="5">
+        <v>0</v>
+      </c>
       <c r="R41" s="1"/>
       <c r="S41" s="5"/>
       <c r="T41" s="5">
@@ -16546,7 +17173,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>784</v>
       </c>
-      <c r="W41" s="5"/>
+      <c r="W41" s="5">
+        <v>0</v>
+      </c>
       <c r="X41" s="1"/>
       <c r="Y41" s="5"/>
       <c r="Z41" s="5">
@@ -16573,7 +17202,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="E43" s="5"/>
+      <c r="E43" s="5">
+        <v>0</v>
+      </c>
       <c r="F43" s="1"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5">
@@ -16588,7 +17219,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K43" s="5"/>
+      <c r="K43" s="5">
+        <v>0</v>
+      </c>
       <c r="L43" s="1"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5">
@@ -16603,7 +17236,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q43" s="5"/>
+      <c r="Q43" s="5">
+        <v>0</v>
+      </c>
       <c r="R43" s="1"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5">
@@ -16618,7 +17253,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W43" s="5"/>
+      <c r="W43" s="5">
+        <v>0</v>
+      </c>
       <c r="X43" s="1"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5">
@@ -16644,7 +17281,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="E44" s="5"/>
+      <c r="E44" s="5">
+        <v>0</v>
+      </c>
       <c r="F44" s="1"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5">
@@ -16659,7 +17298,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K44" s="5"/>
+      <c r="K44" s="5">
+        <v>0</v>
+      </c>
       <c r="L44" s="1"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5">
@@ -16674,7 +17315,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q44" s="5"/>
+      <c r="Q44" s="5">
+        <v>0</v>
+      </c>
       <c r="R44" s="1"/>
       <c r="S44" s="5"/>
       <c r="T44" s="5">
@@ -16689,7 +17332,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W44" s="5"/>
+      <c r="W44" s="5">
+        <v>0</v>
+      </c>
       <c r="X44" s="1"/>
       <c r="Y44" s="5"/>
       <c r="Z44" s="5">
@@ -16715,7 +17360,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="E45" s="5"/>
+      <c r="E45" s="5">
+        <v>0</v>
+      </c>
       <c r="F45" s="1"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5">
@@ -16730,7 +17377,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K45" s="5"/>
+      <c r="K45" s="5">
+        <v>0</v>
+      </c>
       <c r="L45" s="1"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5">
@@ -16745,7 +17394,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q45" s="5"/>
+      <c r="Q45" s="5">
+        <v>0</v>
+      </c>
       <c r="R45" s="1"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5">
@@ -16760,7 +17411,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W45" s="5"/>
+      <c r="W45" s="5">
+        <v>0</v>
+      </c>
       <c r="X45" s="1"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5">
@@ -16786,7 +17439,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="E46" s="5"/>
+      <c r="E46" s="5">
+        <v>0</v>
+      </c>
       <c r="F46" s="1"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5">
@@ -16801,7 +17456,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K46" s="5"/>
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
       <c r="L46" s="1"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5">
@@ -16816,7 +17473,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q46" s="5"/>
+      <c r="Q46" s="5">
+        <v>0</v>
+      </c>
       <c r="R46" s="1"/>
       <c r="S46" s="5"/>
       <c r="T46" s="5">
@@ -16831,7 +17490,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W46" s="5"/>
+      <c r="W46" s="5">
+        <v>0</v>
+      </c>
       <c r="X46" s="1"/>
       <c r="Y46" s="5"/>
       <c r="Z46" s="5">
@@ -16857,7 +17518,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="E47" s="5"/>
+      <c r="E47" s="5">
+        <v>0</v>
+      </c>
       <c r="F47" s="1"/>
       <c r="G47" s="5"/>
       <c r="H47" s="5">
@@ -16872,7 +17535,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K47" s="5"/>
+      <c r="K47" s="5">
+        <v>0</v>
+      </c>
       <c r="L47" s="1"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5">
@@ -16887,7 +17552,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q47" s="5"/>
+      <c r="Q47" s="5">
+        <v>0</v>
+      </c>
       <c r="R47" s="1"/>
       <c r="S47" s="5"/>
       <c r="T47" s="5">
@@ -16902,7 +17569,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W47" s="5"/>
+      <c r="W47" s="5">
+        <v>0</v>
+      </c>
       <c r="X47" s="1"/>
       <c r="Y47" s="5"/>
       <c r="Z47" s="5">
@@ -16928,7 +17597,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="E48" s="5"/>
+      <c r="E48" s="5">
+        <v>0</v>
+      </c>
       <c r="F48" s="1"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5">
@@ -16943,7 +17614,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K48" s="5"/>
+      <c r="K48" s="5">
+        <v>0</v>
+      </c>
       <c r="L48" s="1"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5">
@@ -16958,7 +17631,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q48" s="5"/>
+      <c r="Q48" s="5">
+        <v>0</v>
+      </c>
       <c r="R48" s="1"/>
       <c r="S48" s="5"/>
       <c r="T48" s="5">
@@ -16973,7 +17648,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W48" s="5"/>
+      <c r="W48" s="5">
+        <v>0</v>
+      </c>
       <c r="X48" s="1"/>
       <c r="Y48" s="5"/>
       <c r="Z48" s="5">
@@ -16990,7 +17667,7 @@
         <v>5</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C49" s="5">
         <v>113</v>
@@ -16999,7 +17676,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="E49" s="5"/>
+      <c r="E49" s="5">
+        <v>0</v>
+      </c>
       <c r="F49" s="1"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5">
@@ -17014,7 +17693,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K49" s="5"/>
+      <c r="K49" s="5">
+        <v>0</v>
+      </c>
       <c r="L49" s="1"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5">
@@ -17029,7 +17710,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q49" s="5"/>
+      <c r="Q49" s="5">
+        <v>0</v>
+      </c>
       <c r="R49" s="1"/>
       <c r="S49" s="5"/>
       <c r="T49" s="5">
@@ -17044,7 +17727,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W49" s="5"/>
+      <c r="W49" s="5">
+        <v>0</v>
+      </c>
       <c r="X49" s="1"/>
       <c r="Y49" s="5"/>
       <c r="Z49" s="5">
@@ -17061,7 +17746,7 @@
         <v>5</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C50" s="1">
         <v>113</v>
@@ -17070,7 +17755,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="E50" s="5"/>
+      <c r="E50" s="5">
+        <v>0</v>
+      </c>
       <c r="F50" s="1"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5">
@@ -17085,7 +17772,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K50" s="5"/>
+      <c r="K50" s="5">
+        <v>0</v>
+      </c>
       <c r="L50" s="1"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5">
@@ -17100,7 +17789,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q50" s="5"/>
+      <c r="Q50" s="5">
+        <v>0</v>
+      </c>
       <c r="R50" s="1"/>
       <c r="S50" s="5"/>
       <c r="T50" s="5">
@@ -17115,7 +17806,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W50" s="5"/>
+      <c r="W50" s="5">
+        <v>0</v>
+      </c>
       <c r="X50" s="1"/>
       <c r="Y50" s="5"/>
       <c r="Z50" s="5">
@@ -17141,7 +17834,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="E51" s="5"/>
+      <c r="E51" s="5">
+        <v>0</v>
+      </c>
       <c r="F51" s="1"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5">
@@ -17156,7 +17851,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K51" s="5"/>
+      <c r="K51" s="5">
+        <v>0</v>
+      </c>
       <c r="L51" s="1"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5">
@@ -17171,7 +17868,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q51" s="5"/>
+      <c r="Q51" s="5">
+        <v>0</v>
+      </c>
       <c r="R51" s="1"/>
       <c r="S51" s="5"/>
       <c r="T51" s="5">
@@ -17186,7 +17885,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W51" s="5"/>
+      <c r="W51" s="5">
+        <v>0</v>
+      </c>
       <c r="X51" s="1"/>
       <c r="Y51" s="5"/>
       <c r="Z51" s="5">
@@ -17203,7 +17904,7 @@
         <v>5</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C52" s="5">
         <v>113</v>
@@ -17212,7 +17913,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="E52" s="5"/>
+      <c r="E52" s="5">
+        <v>0</v>
+      </c>
       <c r="F52" s="1"/>
       <c r="G52" s="5"/>
       <c r="H52" s="5">
@@ -17227,7 +17930,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K52" s="5"/>
+      <c r="K52" s="5">
+        <v>0</v>
+      </c>
       <c r="L52" s="1"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5">
@@ -17242,7 +17947,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q52" s="5"/>
+      <c r="Q52" s="5">
+        <v>0</v>
+      </c>
       <c r="R52" s="1"/>
       <c r="S52" s="5"/>
       <c r="T52" s="5">
@@ -17257,7 +17964,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W52" s="5"/>
+      <c r="W52" s="5">
+        <v>0</v>
+      </c>
       <c r="X52" s="1"/>
       <c r="Y52" s="5"/>
       <c r="Z52" s="5">
@@ -17274,7 +17983,7 @@
         <v>5</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C53" s="1">
         <v>113</v>
@@ -17283,7 +17992,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="E53" s="5"/>
+      <c r="E53" s="5">
+        <v>0</v>
+      </c>
       <c r="F53" s="1"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5">
@@ -17298,7 +18009,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="K53" s="5"/>
+      <c r="K53" s="5">
+        <v>0</v>
+      </c>
       <c r="L53" s="1"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5">
@@ -17313,7 +18026,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="Q53" s="5"/>
+      <c r="Q53" s="5">
+        <v>0</v>
+      </c>
       <c r="R53" s="1"/>
       <c r="S53" s="5"/>
       <c r="T53" s="5">
@@ -17328,7 +18043,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>904</v>
       </c>
-      <c r="W53" s="5"/>
+      <c r="W53" s="5">
+        <v>0</v>
+      </c>
       <c r="X53" s="1"/>
       <c r="Y53" s="5"/>
       <c r="Z53" s="5">
@@ -17355,7 +18072,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E55" s="5"/>
+      <c r="E55" s="5">
+        <v>0</v>
+      </c>
       <c r="F55" s="1"/>
       <c r="G55" s="5"/>
       <c r="H55" s="5">
@@ -17370,7 +18089,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K55" s="5"/>
+      <c r="K55" s="5">
+        <v>0</v>
+      </c>
       <c r="L55" s="1"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5">
@@ -17385,7 +18106,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q55" s="5"/>
+      <c r="Q55" s="5">
+        <v>0</v>
+      </c>
       <c r="R55" s="1"/>
       <c r="S55" s="5"/>
       <c r="T55" s="5">
@@ -17400,7 +18123,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W55" s="5"/>
+      <c r="W55" s="5">
+        <v>0</v>
+      </c>
       <c r="X55" s="1"/>
       <c r="Y55" s="5"/>
       <c r="Z55" s="5">
@@ -17426,7 +18151,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E56" s="5"/>
+      <c r="E56" s="5">
+        <v>0</v>
+      </c>
       <c r="F56" s="1"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5">
@@ -17441,7 +18168,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K56" s="5"/>
+      <c r="K56" s="5">
+        <v>0</v>
+      </c>
       <c r="L56" s="1"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5">
@@ -17456,7 +18185,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q56" s="5"/>
+      <c r="Q56" s="5">
+        <v>0</v>
+      </c>
       <c r="R56" s="1"/>
       <c r="S56" s="5"/>
       <c r="T56" s="5">
@@ -17471,7 +18202,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W56" s="5"/>
+      <c r="W56" s="5">
+        <v>0</v>
+      </c>
       <c r="X56" s="1"/>
       <c r="Y56" s="5"/>
       <c r="Z56" s="5">
@@ -17497,7 +18230,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E57" s="5"/>
+      <c r="E57" s="5">
+        <v>0</v>
+      </c>
       <c r="F57" s="1"/>
       <c r="G57" s="5"/>
       <c r="H57" s="5">
@@ -17512,7 +18247,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K57" s="5"/>
+      <c r="K57" s="5">
+        <v>0</v>
+      </c>
       <c r="L57" s="1"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5">
@@ -17527,7 +18264,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q57" s="5"/>
+      <c r="Q57" s="5">
+        <v>0</v>
+      </c>
       <c r="R57" s="1"/>
       <c r="S57" s="5"/>
       <c r="T57" s="5">
@@ -17542,7 +18281,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W57" s="5"/>
+      <c r="W57" s="5">
+        <v>0</v>
+      </c>
       <c r="X57" s="1"/>
       <c r="Y57" s="5"/>
       <c r="Z57" s="5">
@@ -17568,7 +18309,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E58" s="5"/>
+      <c r="E58" s="5">
+        <v>0</v>
+      </c>
       <c r="F58" s="1"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5">
@@ -17583,7 +18326,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K58" s="5"/>
+      <c r="K58" s="5">
+        <v>0</v>
+      </c>
       <c r="L58" s="1"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5">
@@ -17598,7 +18343,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q58" s="5"/>
+      <c r="Q58" s="5">
+        <v>0</v>
+      </c>
       <c r="R58" s="1"/>
       <c r="S58" s="5"/>
       <c r="T58" s="5">
@@ -17613,7 +18360,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W58" s="5"/>
+      <c r="W58" s="5">
+        <v>0</v>
+      </c>
       <c r="X58" s="1"/>
       <c r="Y58" s="5"/>
       <c r="Z58" s="5">
@@ -17639,7 +18388,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E59" s="5"/>
+      <c r="E59" s="5">
+        <v>0</v>
+      </c>
       <c r="F59" s="1"/>
       <c r="G59" s="5"/>
       <c r="H59" s="5">
@@ -17654,7 +18405,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K59" s="5"/>
+      <c r="K59" s="5">
+        <v>0</v>
+      </c>
       <c r="L59" s="1"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5">
@@ -17669,7 +18422,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q59" s="5"/>
+      <c r="Q59" s="5">
+        <v>0</v>
+      </c>
       <c r="R59" s="1"/>
       <c r="S59" s="5"/>
       <c r="T59" s="5">
@@ -17684,7 +18439,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W59" s="5"/>
+      <c r="W59" s="5">
+        <v>0</v>
+      </c>
       <c r="X59" s="1"/>
       <c r="Y59" s="5"/>
       <c r="Z59" s="5">
@@ -17710,7 +18467,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E60" s="5"/>
+      <c r="E60" s="5">
+        <v>0</v>
+      </c>
       <c r="F60" s="1"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5">
@@ -17725,7 +18484,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K60" s="5"/>
+      <c r="K60" s="5">
+        <v>0</v>
+      </c>
       <c r="L60" s="1"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5">
@@ -17740,7 +18501,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q60" s="5"/>
+      <c r="Q60" s="5">
+        <v>0</v>
+      </c>
       <c r="R60" s="1"/>
       <c r="S60" s="5"/>
       <c r="T60" s="5">
@@ -17755,7 +18518,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W60" s="5"/>
+      <c r="W60" s="5">
+        <v>0</v>
+      </c>
       <c r="X60" s="1"/>
       <c r="Y60" s="5"/>
       <c r="Z60" s="5">
@@ -17772,7 +18537,7 @@
         <v>6</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C61" s="5">
         <v>96</v>
@@ -17781,7 +18546,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E61" s="5"/>
+      <c r="E61" s="5">
+        <v>0</v>
+      </c>
       <c r="F61" s="1"/>
       <c r="G61" s="5"/>
       <c r="H61" s="5">
@@ -17796,7 +18563,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K61" s="5"/>
+      <c r="K61" s="5">
+        <v>0</v>
+      </c>
       <c r="L61" s="1"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5">
@@ -17811,7 +18580,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q61" s="5"/>
+      <c r="Q61" s="5">
+        <v>0</v>
+      </c>
       <c r="R61" s="1"/>
       <c r="S61" s="5"/>
       <c r="T61" s="5">
@@ -17826,7 +18597,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W61" s="5"/>
+      <c r="W61" s="5">
+        <v>0</v>
+      </c>
       <c r="X61" s="1"/>
       <c r="Y61" s="5"/>
       <c r="Z61" s="5">
@@ -17843,7 +18616,7 @@
         <v>6</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C62" s="1">
         <v>96</v>
@@ -17852,7 +18625,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E62" s="5"/>
+      <c r="E62" s="5">
+        <v>0</v>
+      </c>
       <c r="F62" s="1"/>
       <c r="G62" s="5"/>
       <c r="H62" s="5">
@@ -17867,7 +18642,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K62" s="5"/>
+      <c r="K62" s="5">
+        <v>0</v>
+      </c>
       <c r="L62" s="1"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5">
@@ -17882,7 +18659,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q62" s="5"/>
+      <c r="Q62" s="5">
+        <v>0</v>
+      </c>
       <c r="R62" s="1"/>
       <c r="S62" s="5"/>
       <c r="T62" s="5">
@@ -17897,7 +18676,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W62" s="5"/>
+      <c r="W62" s="5">
+        <v>0</v>
+      </c>
       <c r="X62" s="1"/>
       <c r="Y62" s="5"/>
       <c r="Z62" s="5">
@@ -17923,7 +18704,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E63" s="5"/>
+      <c r="E63" s="5">
+        <v>0</v>
+      </c>
       <c r="F63" s="1"/>
       <c r="G63" s="5"/>
       <c r="H63" s="5">
@@ -17938,7 +18721,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K63" s="5"/>
+      <c r="K63" s="5">
+        <v>0</v>
+      </c>
       <c r="L63" s="1"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5">
@@ -17953,7 +18738,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q63" s="5"/>
+      <c r="Q63" s="5">
+        <v>0</v>
+      </c>
       <c r="R63" s="1"/>
       <c r="S63" s="5"/>
       <c r="T63" s="5">
@@ -17968,7 +18755,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W63" s="5"/>
+      <c r="W63" s="5">
+        <v>0</v>
+      </c>
       <c r="X63" s="1"/>
       <c r="Y63" s="5"/>
       <c r="Z63" s="5">
@@ -17985,7 +18774,7 @@
         <v>6</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C64" s="5">
         <v>96</v>
@@ -17994,7 +18783,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E64" s="5"/>
+      <c r="E64" s="5">
+        <v>0</v>
+      </c>
       <c r="F64" s="1"/>
       <c r="G64" s="5"/>
       <c r="H64" s="5">
@@ -18009,7 +18800,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K64" s="5"/>
+      <c r="K64" s="5">
+        <v>0</v>
+      </c>
       <c r="L64" s="1"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5">
@@ -18024,7 +18817,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q64" s="5"/>
+      <c r="Q64" s="5">
+        <v>0</v>
+      </c>
       <c r="R64" s="1"/>
       <c r="S64" s="5"/>
       <c r="T64" s="5">
@@ -18039,7 +18834,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W64" s="5"/>
+      <c r="W64" s="5">
+        <v>0</v>
+      </c>
       <c r="X64" s="1"/>
       <c r="Y64" s="5"/>
       <c r="Z64" s="5">
@@ -18056,7 +18853,7 @@
         <v>6</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C65" s="1">
         <v>96</v>
@@ -18065,7 +18862,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="E65" s="5"/>
+      <c r="E65" s="5">
+        <v>0</v>
+      </c>
       <c r="F65" s="1"/>
       <c r="G65" s="5"/>
       <c r="H65" s="5">
@@ -18080,7 +18879,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="K65" s="5"/>
+      <c r="K65" s="5">
+        <v>0</v>
+      </c>
       <c r="L65" s="1"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5">
@@ -18095,7 +18896,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="Q65" s="5"/>
+      <c r="Q65" s="5">
+        <v>0</v>
+      </c>
       <c r="R65" s="1"/>
       <c r="S65" s="5"/>
       <c r="T65" s="5">
@@ -18110,7 +18913,9 @@
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
         <v>768</v>
       </c>
-      <c r="W65" s="5"/>
+      <c r="W65" s="5">
+        <v>0</v>
+      </c>
       <c r="X65" s="1"/>
       <c r="Y65" s="5"/>
       <c r="Z65" s="5">
@@ -18542,7 +19347,7 @@
         <v>7</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C73" s="12"/>
       <c r="D73" s="12">
@@ -18611,7 +19416,7 @@
         <v>7</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C74" s="10"/>
       <c r="D74" s="12">
@@ -18749,7 +19554,7 @@
         <v>7</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C76" s="12"/>
       <c r="D76" s="12">
@@ -18818,7 +19623,7 @@
         <v>7</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C77" s="10"/>
       <c r="D77" s="12">
@@ -19302,7 +20107,7 @@
         <v>8</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C85" s="12"/>
       <c r="D85" s="12">
@@ -19371,7 +20176,7 @@
         <v>8</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C86" s="10"/>
       <c r="D86" s="12">
@@ -19509,7 +20314,7 @@
         <v>8</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C88" s="12"/>
       <c r="D88" s="12">
@@ -19578,7 +20383,7 @@
         <v>8</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="12">
@@ -20062,7 +20867,7 @@
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="12">
@@ -20131,7 +20936,7 @@
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C98" s="10"/>
       <c r="D98" s="12">
@@ -20269,7 +21074,7 @@
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C100" s="10"/>
       <c r="D100" s="12">
@@ -20338,7 +21143,7 @@
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="12">
@@ -20822,7 +21627,7 @@
         <v>10</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="12">
@@ -20891,7 +21696,7 @@
         <v>10</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C110" s="10"/>
       <c r="D110" s="12">
@@ -21029,7 +21834,7 @@
         <v>10</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C112" s="10"/>
       <c r="D112" s="12">
@@ -21098,7 +21903,7 @@
         <v>10</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="12">
@@ -22226,190 +23031,10 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
+    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D67:F77 D79:F89 D91:F101 D115:F122 P2:R2 V2:X2 Z3:AA10 Z12:AA19 Z21:AA29 Z31:AA41 Z43:AA53 Z55:AA65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N67:R77 N79:R89 N91:R101 N103:R113 D43:F53 D55:F65 H3:L10 H12:L19 H21:L29 H31:L41 H43:L53 H55:L65 N3:R10 N12:R19 N21:R29 N31:R41 N43:R53 N55:R65 T3:X10 T12:X19 T21:X29 T31:X41 T43:X53 T55:X65" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -22423,8 +23048,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
